--- a/Book3.xlsx
+++ b/Book3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ElSakka Group\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{855646F5-BEC4-4814-B785-E7A37A61DE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22B195D-A065-420D-A058-B4AFBF219D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B81E1FB2-2453-4C07-91E6-08C8BBF0B782}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B81E1FB2-2453-4C07-91E6-08C8BBF0B782}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -44,9 +43,6 @@
     <t>Perfect 👍 Here’s a Cost–Benefit Analysis Table for the Library Management System (LMS):</t>
   </si>
   <si>
-    <t>Cost–Benefit Analysis – Library Management System</t>
-  </si>
-  <si>
     <t>Estimated Cost</t>
   </si>
   <si>
@@ -171,6 +167,9 @@
   </si>
   <si>
     <t>Payback Period: Approximately 1.3–2.6 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online Food Ordering System </t>
   </si>
 </sst>
 </file>
@@ -543,172 +542,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E51A24-A7FA-46DE-939E-7768E7D5372D}">
   <dimension ref="AD1:AW33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="36" max="36" width="58" customWidth="1"/>
-    <col min="42" max="42" width="14.44140625" customWidth="1"/>
+    <col min="42" max="42" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="30:49" x14ac:dyDescent="0.3">
+    <row r="1" spans="30:49" x14ac:dyDescent="0.25">
       <c r="AD1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AM9" t="s">
+    <row r="7" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AN7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AW10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AL11" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AW10" t="s">
+      <c r="AQ11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AL11" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM11" t="s">
+      <c r="AW11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AL12" t="s">
         <v>4</v>
       </c>
-      <c r="AP11" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AW11" t="s">
+      <c r="AM12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AL12" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM12" t="s">
+      <c r="AW12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AL13" t="s">
         <v>6</v>
       </c>
-      <c r="AP12" t="s">
+      <c r="AM13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP13" t="s">
         <v>36</v>
       </c>
-      <c r="AQ12" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW12" t="s">
+      <c r="AQ13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AL13" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM13" t="s">
+      <c r="AW13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AL14" t="s">
         <v>8</v>
       </c>
-      <c r="AP13" t="s">
+      <c r="AM14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP14" t="s">
         <v>37</v>
       </c>
-      <c r="AQ13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW13" t="s">
+      <c r="AQ14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AL14" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM14" t="s">
+      <c r="AW14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AL15" t="s">
         <v>10</v>
       </c>
-      <c r="AP14" t="s">
+      <c r="AM15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP15" t="s">
         <v>38</v>
       </c>
-      <c r="AQ14" t="s">
-        <v>25</v>
-      </c>
-      <c r="AW14" t="s">
+      <c r="AQ15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AL15" t="s">
-        <v>11</v>
-      </c>
-      <c r="AM15" t="s">
+      <c r="AW15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="30:49" x14ac:dyDescent="0.25">
+      <c r="AL16" t="s">
         <v>12</v>
       </c>
-      <c r="AP15" t="s">
+      <c r="AM16" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP16" t="s">
         <v>39</v>
       </c>
-      <c r="AQ15" t="s">
-        <v>27</v>
-      </c>
-      <c r="AW15" t="s">
+      <c r="AQ16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="30:49" x14ac:dyDescent="0.3">
-      <c r="AL16" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM16" t="s">
+      <c r="AW16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="38:43" x14ac:dyDescent="0.25">
+      <c r="AL17" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP17" t="s">
         <v>14</v>
       </c>
-      <c r="AP16" t="s">
+      <c r="AQ17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="38:43" x14ac:dyDescent="0.25">
+      <c r="AN27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="38:43" x14ac:dyDescent="0.25">
+      <c r="AN29" t="s">
+        <v>32</v>
+      </c>
+      <c r="AP29" t="s">
         <v>40</v>
       </c>
-      <c r="AQ16" t="s">
-        <v>29</v>
-      </c>
-      <c r="AW16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="38:43" x14ac:dyDescent="0.3">
-      <c r="AL17" t="s">
-        <v>16</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>17</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="38:43" x14ac:dyDescent="0.3">
-      <c r="AN27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="38:43" x14ac:dyDescent="0.3">
-      <c r="AN29" t="s">
+    </row>
+    <row r="30" spans="38:43" x14ac:dyDescent="0.25">
+      <c r="AN30" t="s">
         <v>33</v>
       </c>
-      <c r="AP29" t="s">
+      <c r="AQ30" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="38:43" x14ac:dyDescent="0.3">
-      <c r="AN30" t="s">
+    <row r="31" spans="38:43" x14ac:dyDescent="0.25">
+      <c r="AN31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="40:40" x14ac:dyDescent="0.25">
+      <c r="AN33" t="s">
         <v>34</v>
-      </c>
-      <c r="AQ30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="38:43" x14ac:dyDescent="0.3">
-      <c r="AN31" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="40:40" x14ac:dyDescent="0.3">
-      <c r="AN33" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
